--- a/demo/sov/attachments/01_acme_SOV.xlsx
+++ b/demo/sov/attachments/01_acme_SOV.xlsx
@@ -211,6 +211,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -660,10 +663,8 @@
           <t>Number of Locations</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>22 (+3 see embedded image below)</t>
-        </is>
+      <c r="B13" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="14">
